--- a/ExcelPruebas.xlsx
+++ b/ExcelPruebas.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oracle-my.sharepoint.com/personal/laura_barrera_rincon_oracle_com/Documents/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAURAB~1\AppData\Local\Temp\Mxt254\mx86_64b\RemoteFiles\67386_11_29\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{F6FB8B53-76E4-41D2-A847-E56163B98B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD21EEE8-8C29-444A-B2CF-1E173FE94DD6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC58AF2-0600-4BC7-822E-C02D0320CA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{21206F7A-665E-4522-98AC-2BE7A21F2C6E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Z$16</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1076,7 +1079,7 @@
         <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
         <v>41</v>
@@ -1150,7 +1153,7 @@
         <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
         <v>29</v>
@@ -1224,7 +1227,7 @@
         <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -1298,7 +1301,7 @@
         <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s">
         <v>29</v>
@@ -1882,6 +1885,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Z16" xr:uid="{9DCE6DD7-A97E-497E-BABD-E75A1E45644C}"/>
   <hyperlinks>
     <hyperlink ref="I8" r:id="rId1" xr:uid="{A07842B1-2BB1-4296-B7D6-F52B3609A5E2}"/>
     <hyperlink ref="I7" r:id="rId2" xr:uid="{88FDE106-304B-4A9C-951D-FA130CEA2779}"/>
